--- a/data/trans_dic/IP1021_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP1021_2023-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen dolor crónico</t>
+          <t>Menores que padecen dolor crónico (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,28</t>
+          <t>0,0; 4,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,68</t>
+          <t>0,0; 9,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,33; 6,38</t>
+          <t>0,33; 5,76</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,27</t>
+          <t>1,1; 3,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,44</t>
+          <t>0,51; 2,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,25</t>
+          <t>0,96; 2,28</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,95; 4,91</t>
+          <t>1,02; 5,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,04; 6,4</t>
+          <t>0,84; 6,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,33; 4,73</t>
+          <t>1,49; 4,72</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,04</t>
+          <t>1,25; 3,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,83</t>
+          <t>0,93; 2,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 2,57</t>
+          <t>1,27; 2,49</t>
         </is>
       </c>
     </row>
@@ -752,4 +753,380 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen dolor crónico (tasa de respuesta: 99,95%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>391</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1815</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2207</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2423</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5994</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>382; 6719</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>8963</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6002</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>14965</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>5079; 14941</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2639; 11754</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>9327; 22273</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>3730</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4926</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>8656</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>1523; 8121</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1532; 11635</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>4964; 15691</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>13084</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>12743</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>25827</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>8293; 20644</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>7113; 21086</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>18158; 35425</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1021_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP1021_2023-Estudios-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,43</t>
+          <t>0,0; 4,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,67</t>
+          <t>0,0; 10,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,33; 5,76</t>
+          <t>0,34; 5,96</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,1; 3,25</t>
+          <t>1,16; 3,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,28</t>
+          <t>0,51; 2,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,96; 2,28</t>
+          <t>0,96; 2,25</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,02; 5,43</t>
+          <t>0,99; 5,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,84; 6,36</t>
+          <t>0,93; 6,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,49; 4,72</t>
+          <t>1,31; 4,55</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,11</t>
+          <t>1,28; 2,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,77</t>
+          <t>0,96; 2,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,49</t>
+          <t>1,23; 2,5</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2423</t>
+          <t>0; 2273</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 5994</t>
+          <t>0; 6782</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>382; 6719</t>
+          <t>391; 6951</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5079; 14941</t>
+          <t>5348; 14793</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2639; 11754</t>
+          <t>2612; 12146</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9327; 22273</t>
+          <t>9409; 22005</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1523; 8121</t>
+          <t>1488; 8034</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1532; 11635</t>
+          <t>1707; 11411</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4964; 15691</t>
+          <t>4354; 15113</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8293; 20644</t>
+          <t>8530; 19738</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7113; 21086</t>
+          <t>7345; 20776</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18158; 35425</t>
+          <t>17572; 35623</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1021_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP1021_2023-Estudios-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,16</t>
+          <t>0,0; 10,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,94</t>
+          <t>0,0; 4,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,34; 5,96</t>
+          <t>0,33; 6,15</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,22</t>
+          <t>0,51; 2,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,35</t>
+          <t>1,24; 3,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,96; 2,25</t>
+          <t>1,02; 2,4</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2,55%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
           <t>2,49%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>2,69%</t>
-        </is>
-      </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,99; 5,37</t>
+          <t>0,98; 5,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 6,24</t>
+          <t>0,94; 4,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,31; 4,55</t>
+          <t>1,29; 4,53</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,97</t>
+          <t>0,95; 2,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,96; 2,73</t>
+          <t>1,32; 3,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,23; 2,5</t>
+          <t>1,27; 2,61</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>1537</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1815</t>
+          <t>340</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>1877</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2273</t>
+          <t>0; 5855</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 6782</t>
+          <t>0; 2092</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>391; 6951</t>
+          <t>341; 6363</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>8963</t>
+          <t>5438</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6002</t>
+          <t>9163</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14965</t>
+          <t>14601</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5348; 14793</t>
+          <t>2422; 11969</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2612; 12146</t>
+          <t>5337; 14925</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9409; 22005</t>
+          <t>9290; 21732</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3730</t>
+          <t>4288</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4926</t>
+          <t>3733</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8656</t>
+          <t>8021</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1488; 8034</t>
+          <t>1641; 9829</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1707; 11411</t>
+          <t>1406; 7410</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4354; 15113</t>
+          <t>4085; 14386</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>22</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>13084</t>
+          <t>11263</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>12743</t>
+          <t>13236</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>25827</t>
+          <t>24500</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8530; 19738</t>
+          <t>6666; 19304</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7345; 20776</t>
+          <t>8299; 20482</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17572; 35623</t>
+          <t>16855; 34672</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1021_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP1021_2023-Estudios-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,290 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que padecen dolor crónico (tasa de respuesta: 99,95%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Primarios</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>2,71%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,81%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 10,32</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,47</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,33; 6,15</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2,12%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>0,51; 2,52</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>1,24; 3,46</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1,02; 2,4</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>2,49%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2,52%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>0,98; 5,86</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,94; 4,94</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>1,29; 4,53</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2,11%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>0,95; 2,76</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>1,32; 3,26</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1,27; 2,61</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -828,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.02709580093254403</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.007277476049971831</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.0181417095613584</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>1537</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1877</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.003295014106423739</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0; 5855</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0; 2092</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>341; 6363</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.1032070058790763</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.04473967302687182</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.06148105860248582</v>
       </c>
     </row>
     <row r="7">
@@ -901,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.01143182956157985</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.02123065318282428</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.01609322374859018</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>5438</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>9163</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>14601</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.005091495637755255</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.01236642462466761</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.01023989957175883</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>2422; 11969</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>5337; 14925</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>9290; 21732</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.02516294401644698</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.03458058059291166</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.0239530325854787</v>
       </c>
     </row>
     <row r="10">
@@ -974,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.02554702155559037</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.02488940465567735</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.02523671638226244</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>4288</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>3733</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>8021</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.009776507338399479</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.009376415502766172</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.01285150016717399</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>1641; 9829</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1406; 7410</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>4085; 14386</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.05855248648816924</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.04940645554801874</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.04526139884726781</v>
       </c>
     </row>
     <row r="13">
@@ -1047,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.01608439139545351</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.02106562526225293</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.01844015475089064</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>11263</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>13236</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>24500</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.009519442113418772</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.01320846616561259</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.01268583665667685</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>6666; 19304</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>8299; 20482</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>16855; 34672</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.02756616270834144</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.03259677869523581</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.02609656053516779</v>
       </c>
     </row>
     <row r="16">
@@ -1129,4 +781,376 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen dolor crónico (tasa de respuesta: 99,95%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>1537</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>340</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>1877</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>5855</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>2092</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>6363</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>5438</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>9163</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>14601</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>2422</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>5337</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>9290</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>11969</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>14925</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>21732</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>4288</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>3733</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>8021</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>1641</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>1406</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>4085</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>9829</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>7410</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>14386</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>11263</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>13236</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>24500</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>6666</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>8299</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>16855</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>19304</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>20482</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>34672</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>